--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_13_Monitoring, Logging _ Observability/Day_13_Phan_02_19_Cau.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>60</v>
@@ -749,7 +749,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Correlation, Provider/model/version.</t>
+          <t>Tập trường tối thiểu cần thiết để debug độ trễ và chi phí theo model/prompt mà không làm rò rỉ PII: Mã định danh tương quan, phiên bản prompt/model, số lượng token, thời gian xử lý và kết quả thực thi.</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>60</v>
@@ -857,7 +857,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Pre-render redaction, Regex và entity recognition.</t>
+          <t>Nguyên tắc che dữ liệu nhạy cảm (PII redaction): Việc làm sạch dữ liệu phải được thực hiện tại ranh giới ứng dụng trước khi phát đi (redact-before-emission), ngăn chặn PII lọt vào bất kỳ bộ đệm trace hay log nào.</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G12" s="3" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4" t="n">
         <v>60</v>
@@ -1116,7 +1116,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Execution context, Context binding.</t>
+          <t>Trong các ứng dụng bất đồng bộ chạy nhiều coroutines, dữ liệu ngữ cảnh của người dùng phải được cô lập độc lập theo từng task (sử dụng `contextvars.ContextVar`) để tránh tình trạng race-condition gây lẫn lộn thông tin tenant.</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99100</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1164,7 +1164,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách error khỏi normal trước khi áp sampling rate.</t>
+          <t>Tổng số event giữ lại: Error events (100% của 1% * 1.000.000 = 10.000) + Normal events (9% của 99% * 1.000.000 = 0,09 * 990.000 = 89.100). Tổng cộng: 10.000 + 89.100 = 99.100 event.</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1272,7 +1272,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Trace identity, Root/child span.</t>
+          <t>Trong kiến trúc microservices và hàng đợi async, trace context bắt buộc phải được truyền (propagate) và liên kết xuyên suốt qua các message queue để bảo đảm quan hệ nhân quả (causality) giữa các span.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I16" s="4" t="n">
         <v>60</v>
@@ -1320,7 +1320,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Root invocation, Model generation span.</t>
+          <t>Thiết kế span hữu ích cho agent loop: Nên phân tách span theo từng tác vụ thao tác cụ thể (plan, retrieve, model call, tool execution, retry) thay vì gom toàn bộ vào một span duy nhất hoặc chia vụn theo từng token.</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I19" s="4" t="n">
@@ -1478,7 +1478,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn các rule dùng outcome nhưng không mở rộng data risk.</t>
+          <t>Chính sách tail-sampling hiệu quả khi lưu lượng lớn và buffer hữu hạn: (a) Giữ lại 100% các vết có lỗi, độ trễ cao hoặc chi phí bất thường, (b) lấy mẫu lưu lượng bình thường theo ngân sách cố định, (c) đặt giới hạn buffer để chống tràn bộ nhớ và ghi nhận rõ tỷ lệ lấy mẫu.</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G20" s="3" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20" s="4" t="n">
         <v>60</v>
@@ -1526,7 +1526,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Sequential dependency, External waiting.</t>
+          <t>Biểu đồ waterfall cho thấy tool A và tool B chạy tuần tự mất 2s + 2s dù hoàn toàn độc lập; mẫu hình tắc nghẽn là thực thi nối tiếp (serial execution) và giải pháp tối ưu là chạy song song hai công cụ.</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" s="4" t="n">
         <v>60</v>
@@ -1574,7 +1574,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Prompt name/label/version, Resolved source.</t>
+          <t>Nhãn 'production' là tham chiếu động; để bảo đảm khả năng kiểm toán và phục hồi chính xác, hệ thống telemetry bắt buộc phải ghi lại mã băm (hash) hoặc số phiên bản cụ thể của prompt đã được phân giải.</t>
         </is>
       </c>
     </row>
